--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ12"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.010645</v>
+        <v>-0.0133</v>
       </c>
       <c r="E2">
-        <v>0.1522</v>
+        <v>0.03736</v>
       </c>
       <c r="G2">
-        <v>0.1713963887087415</v>
+        <v>0.2260232536156536</v>
       </c>
       <c r="H2">
-        <v>0.1713963887087415</v>
+        <v>0.2260232536156536</v>
       </c>
       <c r="I2">
-        <v>0.1729050756050108</v>
+        <v>0.1306172606106437</v>
       </c>
       <c r="J2">
-        <v>0.1727442034436059</v>
+        <v>0.1306164439975733</v>
       </c>
       <c r="K2">
-        <v>235.32</v>
+        <v>133.45</v>
       </c>
       <c r="L2">
-        <v>0.1606444345837458</v>
+        <v>0.126146138576425</v>
       </c>
       <c r="M2">
-        <v>112.88</v>
+        <v>118.3</v>
       </c>
       <c r="N2">
-        <v>0.05230284496339543</v>
+        <v>0.06422018348623852</v>
       </c>
       <c r="O2">
-        <v>0.4796872344042155</v>
+        <v>0.8864743349569125</v>
       </c>
       <c r="P2">
-        <v>112.88</v>
+        <v>118.3</v>
       </c>
       <c r="Q2">
-        <v>0.05230284496339543</v>
+        <v>0.06422018348623852</v>
       </c>
       <c r="R2">
-        <v>0.4796872344042155</v>
+        <v>0.8864743349569125</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>366.16</v>
+        <v>291.156</v>
       </c>
       <c r="V2">
-        <v>0.1696599017699935</v>
+        <v>0.1580565658759025</v>
       </c>
       <c r="W2">
-        <v>0.09995023613020956</v>
+        <v>0.04036535061873895</v>
       </c>
       <c r="X2">
-        <v>0.04757277803263578</v>
+        <v>0.08056212598559234</v>
       </c>
       <c r="Y2">
-        <v>0.05237745809757378</v>
+        <v>-0.04019677536685339</v>
       </c>
       <c r="Z2">
-        <v>0.848265885911901</v>
+        <v>0.6071932222106793</v>
       </c>
       <c r="AA2">
-        <v>0.1344084623839203</v>
+        <v>0.04389248043552229</v>
       </c>
       <c r="AB2">
-        <v>0.04707228550016244</v>
+        <v>0.08042878936996081</v>
       </c>
       <c r="AC2">
-        <v>0.08706828466613703</v>
+        <v>-0.03631547029079178</v>
       </c>
       <c r="AD2">
-        <v>146.412</v>
+        <v>155.41</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>146.412</v>
+        <v>155.41</v>
       </c>
       <c r="AG2">
-        <v>-219.748</v>
+        <v>-135.746</v>
       </c>
       <c r="AH2">
-        <v>0.06352999984379151</v>
+        <v>0.07780186331983319</v>
       </c>
       <c r="AI2">
-        <v>0.06413106895627356</v>
+        <v>0.07792279420981643</v>
       </c>
       <c r="AJ2">
-        <v>-0.1133626213081366</v>
+        <v>-0.07955324627832208</v>
       </c>
       <c r="AK2">
-        <v>-0.1146400452408428</v>
+        <v>-0.07969803681658755</v>
       </c>
       <c r="AL2">
-        <v>3.819</v>
+        <v>2.958</v>
       </c>
       <c r="AM2">
-        <v>3.819</v>
+        <v>2.958</v>
       </c>
       <c r="AN2">
-        <v>0.5583555792845702</v>
+        <v>1.029887342611001</v>
       </c>
       <c r="AO2">
-        <v>66.3210264467138</v>
+        <v>46.71399594320486</v>
       </c>
       <c r="AP2">
-        <v>-0.8380291358401344</v>
+        <v>-0.8995758780649437</v>
       </c>
       <c r="AQ2">
-        <v>66.3210264467138</v>
+        <v>46.71399594320486</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0663</v>
+        <v>0.0607</v>
       </c>
       <c r="E3">
-        <v>0.247</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="G3">
-        <v>0.2285123966942149</v>
+        <v>0.2423933020216459</v>
       </c>
       <c r="H3">
-        <v>0.2285123966942149</v>
+        <v>0.2423933020216459</v>
       </c>
       <c r="I3">
-        <v>0.2477272727272727</v>
+        <v>0.1917500510516643</v>
       </c>
       <c r="J3">
-        <v>0.2477186411149826</v>
+        <v>0.1917416593645286</v>
       </c>
       <c r="K3">
-        <v>114.8</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L3">
-        <v>0.2371900826446281</v>
+        <v>0.1866448846232387</v>
       </c>
       <c r="M3">
-        <v>54.3</v>
+        <v>62.1</v>
       </c>
       <c r="N3">
-        <v>0.05222660382802731</v>
+        <v>0.06453959675743089</v>
       </c>
       <c r="O3">
-        <v>0.4729965156794425</v>
+        <v>0.6794310722100656</v>
       </c>
       <c r="P3">
-        <v>54.3</v>
+        <v>62.1</v>
       </c>
       <c r="Q3">
-        <v>0.05222660382802731</v>
+        <v>0.06453959675743089</v>
       </c>
       <c r="R3">
-        <v>0.4729965156794425</v>
+        <v>0.6794310722100656</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,55 +770,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>164.8</v>
+        <v>161.7</v>
       </c>
       <c r="V3">
-        <v>0.1585072617101087</v>
+        <v>0.1680523799625857</v>
       </c>
       <c r="W3">
-        <v>0.177516622854492</v>
+        <v>0.1236137408709765</v>
       </c>
       <c r="X3">
-        <v>0.04756623417210915</v>
+        <v>0.08056212598559234</v>
       </c>
       <c r="Y3">
-        <v>0.1299503886823829</v>
+        <v>0.04305161488538414</v>
       </c>
       <c r="Z3">
-        <v>0.9952704092124202</v>
+        <v>0.8288761002031144</v>
       </c>
       <c r="AA3">
-        <v>0.2465470333120534</v>
+        <v>0.1589300788605444</v>
       </c>
       <c r="AB3">
-        <v>0.04707970341207184</v>
+        <v>0.08042878936996081</v>
       </c>
       <c r="AC3">
-        <v>0.1994673298999816</v>
+        <v>0.0785012894905836</v>
       </c>
       <c r="AD3">
-        <v>16.2</v>
+        <v>8.23</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>16.2</v>
+        <v>8.23</v>
       </c>
       <c r="AG3">
-        <v>-148.6</v>
+        <v>-153.47</v>
       </c>
       <c r="AH3">
-        <v>0.01534236196609527</v>
+        <v>0.008480776562966932</v>
       </c>
       <c r="AI3">
-        <v>0.02143991529910005</v>
+        <v>0.01155687865979526</v>
       </c>
       <c r="AJ3">
-        <v>-0.1667601840421951</v>
+        <v>-0.1897666712005243</v>
       </c>
       <c r="AK3">
-        <v>-0.2515233581584293</v>
+        <v>-0.2788183783587377</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -827,10 +827,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.1308562197092084</v>
+        <v>0.08304742684157418</v>
       </c>
       <c r="AP3">
-        <v>-1.20032310177706</v>
+        <v>-1.548637739656912</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abu Dhabi National Takaful Company PSC (ADX:TKFL)</t>
+          <t>National General Insurance Co. (P.J.S.C.) (DFM:NGI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,46 +850,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0265</v>
+        <v>0.0194</v>
       </c>
       <c r="E4">
-        <v>0.0574</v>
+        <v>0.12</v>
       </c>
       <c r="G4">
-        <v>0.2874251497005988</v>
+        <v>0.1993927125506073</v>
       </c>
       <c r="H4">
-        <v>0.2874251497005988</v>
+        <v>0.1993927125506073</v>
       </c>
       <c r="I4">
-        <v>0.2614770459081836</v>
+        <v>0.1609311740890688</v>
       </c>
       <c r="J4">
-        <v>0.2614770459081836</v>
+        <v>0.1609311740890688</v>
       </c>
       <c r="K4">
-        <v>20.6</v>
+        <v>15.9</v>
       </c>
       <c r="L4">
-        <v>0.4111776447105789</v>
+        <v>0.1609311740890688</v>
       </c>
       <c r="M4">
-        <v>5.44</v>
+        <v>12.2</v>
       </c>
       <c r="N4">
-        <v>0.03243887895050687</v>
+        <v>0.09166040570999248</v>
       </c>
       <c r="O4">
-        <v>0.2640776699029126</v>
+        <v>0.7672955974842767</v>
       </c>
       <c r="P4">
-        <v>5.44</v>
+        <v>12.2</v>
       </c>
       <c r="Q4">
-        <v>0.03243887895050687</v>
+        <v>0.09166040570999248</v>
       </c>
       <c r="R4">
-        <v>0.2640776699029126</v>
+        <v>0.7672955974842767</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,55 +898,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>37.9</v>
+        <v>9.75</v>
       </c>
       <c r="V4">
-        <v>0.2259988073941562</v>
+        <v>0.07325319308790383</v>
       </c>
       <c r="W4">
-        <v>0.1772805507745267</v>
+        <v>0.1129261363636364</v>
       </c>
       <c r="X4">
-        <v>0.04742175863259864</v>
+        <v>0.08020795072631406</v>
       </c>
       <c r="Y4">
-        <v>0.129858792141928</v>
+        <v>0.03271818563732229</v>
       </c>
       <c r="Z4">
-        <v>0.7190011481056257</v>
+        <v>0.8288590604026845</v>
       </c>
       <c r="AA4">
-        <v>0.1880022962112514</v>
+        <v>0.1333892617449664</v>
       </c>
       <c r="AB4">
-        <v>0.04724524497297677</v>
+        <v>0.08020795072631406</v>
       </c>
       <c r="AC4">
-        <v>0.1407570512382746</v>
+        <v>0.05318131101865237</v>
       </c>
       <c r="AD4">
-        <v>0.9429999999999999</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.9429999999999999</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>-36.957</v>
+        <v>-9.75</v>
       </c>
       <c r="AH4">
-        <v>0.00559169369615104</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.006901195085002525</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.2826690530276956</v>
+        <v>-0.0790433725172274</v>
       </c>
       <c r="AK4">
-        <v>-0.3742746321258216</v>
+        <v>-0.07520246818357115</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -955,10 +955,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>0.06985185185185185</v>
+        <v>0</v>
       </c>
       <c r="AP4">
-        <v>-2.737555555555556</v>
+        <v>-0.6018518518518519</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +969,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>National Takaful Company (Watania) P.J.S.C. (ADX:WATANIA)</t>
+          <t>Union Insurance Company P.J.S.C. (ADX:UNION)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -978,118 +978,112 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.158</v>
+        <v>-0.0441</v>
+      </c>
+      <c r="E5">
+        <v>0.132</v>
       </c>
       <c r="G5">
-        <v>0.1075862068965517</v>
+        <v>0.04584103512014787</v>
       </c>
       <c r="H5">
-        <v>0.1075862068965517</v>
+        <v>0.04584103512014787</v>
       </c>
       <c r="I5">
-        <v>0.05672413793103449</v>
+        <v>0.04103512014787431</v>
       </c>
       <c r="J5">
-        <v>0.05672413793103449</v>
+        <v>0.04103512014787431</v>
       </c>
       <c r="K5">
-        <v>2.27</v>
+        <v>4.44</v>
       </c>
       <c r="L5">
-        <v>0.03913793103448276</v>
+        <v>0.04103512014787431</v>
       </c>
       <c r="M5">
-        <v>3.06</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.07500000000000001</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>1.348017621145374</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>3.06</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.07500000000000001</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>1.348017621145374</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>11.6</v>
+        <v>43.7</v>
       </c>
       <c r="V5">
-        <v>0.2843137254901961</v>
+        <v>0.7680140597539544</v>
       </c>
       <c r="W5">
-        <v>0.08832684824902724</v>
+        <v>0.06666666666666668</v>
       </c>
       <c r="X5">
-        <v>0.0478131126776875</v>
+        <v>0.08172163328362045</v>
       </c>
       <c r="Y5">
-        <v>0.04051373557133974</v>
+        <v>-0.01505496661695377</v>
       </c>
       <c r="Z5">
-        <v>3.27683615819209</v>
+        <v>1.756522021461388</v>
       </c>
       <c r="AA5">
-        <v>0.1858757062146893</v>
+        <v>0.0720790921930551</v>
       </c>
       <c r="AB5">
-        <v>0.04680421714043607</v>
+        <v>0.08099226759939497</v>
       </c>
       <c r="AC5">
-        <v>0.1390714890742532</v>
+        <v>-0.008913175406339874</v>
       </c>
       <c r="AD5">
-        <v>1.33</v>
+        <v>2.08</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.33</v>
+        <v>2.08</v>
       </c>
       <c r="AG5">
-        <v>-10.27</v>
+        <v>-41.62</v>
       </c>
       <c r="AH5">
-        <v>0.03156895323997152</v>
+        <v>0.03526619192946762</v>
       </c>
       <c r="AI5">
-        <v>0.04399603043334437</v>
+        <v>0.02838427947598253</v>
       </c>
       <c r="AJ5">
-        <v>-0.3363904356370783</v>
+        <v>-2.723821989528797</v>
       </c>
       <c r="AK5">
-        <v>-0.5512614063338701</v>
+        <v>-1.407031778228533</v>
       </c>
       <c r="AL5">
-        <v>0.099</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>0.099</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>0.4054878048780488</v>
-      </c>
-      <c r="AO5">
-        <v>33.23232323232323</v>
+        <v>0.3586206896551725</v>
       </c>
       <c r="AP5">
-        <v>-3.13109756097561</v>
-      </c>
-      <c r="AQ5">
-        <v>33.23232323232323</v>
+        <v>-7.175862068965518</v>
       </c>
     </row>
     <row r="6">
@@ -1100,7 +1094,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>National General Insurance Co. (P.J.S.C.) (DFM:NGI)</t>
+          <t>Al Ain Ahlia Insurance Company P.S.C. (ADX:ALAIN)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1109,46 +1103,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.008489999999999999</v>
+        <v>-0.0441</v>
       </c>
       <c r="E6">
-        <v>0.251</v>
+        <v>0.00522</v>
       </c>
       <c r="G6">
-        <v>0.1248799231508165</v>
+        <v>0.2721649484536082</v>
       </c>
       <c r="H6">
-        <v>0.1248799231508165</v>
+        <v>0.2721649484536082</v>
       </c>
       <c r="I6">
-        <v>0.1902017291066282</v>
+        <v>0.1329896907216495</v>
       </c>
       <c r="J6">
-        <v>0.1902017291066282</v>
+        <v>0.1329896907216495</v>
       </c>
       <c r="K6">
-        <v>19.8</v>
+        <v>13.7</v>
       </c>
       <c r="L6">
-        <v>0.1902017291066282</v>
+        <v>0.1412371134020619</v>
       </c>
       <c r="M6">
-        <v>6.12</v>
+        <v>12.3</v>
       </c>
       <c r="N6">
-        <v>0.04803767660910518</v>
+        <v>0.09124629080118694</v>
       </c>
       <c r="O6">
-        <v>0.3090909090909091</v>
+        <v>0.8978102189781023</v>
       </c>
       <c r="P6">
-        <v>6.12</v>
+        <v>12.3</v>
       </c>
       <c r="Q6">
-        <v>0.04803767660910518</v>
+        <v>0.09124629080118694</v>
       </c>
       <c r="R6">
-        <v>0.3090909090909091</v>
+        <v>0.8978102189781023</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1157,67 +1151,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>23.7</v>
+        <v>31.1</v>
       </c>
       <c r="V6">
-        <v>0.1860282574568289</v>
+        <v>0.2307121661721068</v>
       </c>
       <c r="W6">
-        <v>0.1548084440969507</v>
+        <v>0.04036535061873895</v>
       </c>
       <c r="X6">
-        <v>0.04757932189316241</v>
+        <v>0.08020795072631406</v>
       </c>
       <c r="Y6">
-        <v>0.1072291222037883</v>
+        <v>-0.03984260010757511</v>
       </c>
       <c r="Z6">
-        <v>0.8683683683683684</v>
+        <v>0.3300442327322219</v>
       </c>
       <c r="AA6">
-        <v>0.1651651651651652</v>
+        <v>0.04389248043552229</v>
       </c>
       <c r="AB6">
-        <v>0.04706486758825304</v>
+        <v>0.08020795072631406</v>
       </c>
       <c r="AC6">
-        <v>0.1181002975769121</v>
+        <v>-0.03631547029079178</v>
       </c>
       <c r="AD6">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>-21.6</v>
+        <v>-31.1</v>
       </c>
       <c r="AH6">
-        <v>0.01621621621621622</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>0.01469559132260322</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-0.2041587901701323</v>
+        <v>-0.2999035679845709</v>
       </c>
       <c r="AK6">
-        <v>-0.1812080536912751</v>
+        <v>-0.09776799748506761</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>0.228</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>0.228</v>
       </c>
       <c r="AN6">
-        <v>0.103960396039604</v>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>56.57894736842105</v>
       </c>
       <c r="AP6">
-        <v>-1.069306930693069</v>
+        <v>-1.851190476190476</v>
+      </c>
+      <c r="AQ6">
+        <v>56.57894736842105</v>
       </c>
     </row>
     <row r="7">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dubai National Insurance &amp; Reinsurance Co. (P.S.C.) (DFM:DNIR)</t>
+          <t>Al Wathba National Insurance Company PJSC (ADX:AWNIC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1237,46 +1237,46 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0128</v>
+        <v>0.0357</v>
       </c>
       <c r="E7">
-        <v>0.0258</v>
+        <v>-0.17</v>
       </c>
       <c r="G7">
-        <v>0.3842364532019704</v>
+        <v>0.7087628865979382</v>
       </c>
       <c r="H7">
-        <v>0.3842364532019704</v>
+        <v>0.7087628865979382</v>
       </c>
       <c r="I7">
-        <v>0.3325123152709359</v>
+        <v>0.1778350515463918</v>
       </c>
       <c r="J7">
-        <v>0.3325123152709359</v>
+        <v>0.1778350515463918</v>
       </c>
       <c r="K7">
-        <v>13.5</v>
+        <v>6.14</v>
       </c>
       <c r="L7">
-        <v>0.3325123152709359</v>
+        <v>0.07912371134020618</v>
       </c>
       <c r="M7">
-        <v>9.43</v>
+        <v>11.3</v>
       </c>
       <c r="N7">
-        <v>0.04997350291467938</v>
+        <v>0.04494828957836118</v>
       </c>
       <c r="O7">
-        <v>0.6985185185185185</v>
+        <v>1.840390879478828</v>
       </c>
       <c r="P7">
-        <v>9.43</v>
+        <v>11.3</v>
       </c>
       <c r="Q7">
-        <v>0.04997350291467938</v>
+        <v>0.04494828957836118</v>
       </c>
       <c r="R7">
-        <v>0.6985185185185185</v>
+        <v>1.840390879478828</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1285,67 +1285,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>34.7</v>
+        <v>24.4</v>
       </c>
       <c r="V7">
-        <v>0.1838897721250663</v>
+        <v>0.09705648369132855</v>
       </c>
       <c r="W7">
-        <v>0.1017332328560663</v>
+        <v>0.02386319471434123</v>
       </c>
       <c r="X7">
-        <v>0.04734017771778325</v>
+        <v>0.09518003792210541</v>
       </c>
       <c r="Y7">
-        <v>0.05439305513828307</v>
+        <v>-0.07131684320776419</v>
       </c>
       <c r="Z7">
-        <v>0.4451754385964913</v>
+        <v>0.2303354111012169</v>
       </c>
       <c r="AA7">
-        <v>0.1480263157894737</v>
+        <v>0.04096170970614425</v>
       </c>
       <c r="AB7">
-        <v>0.04734017771778325</v>
+        <v>0.08406911830022717</v>
       </c>
       <c r="AC7">
-        <v>0.1006861380716904</v>
+        <v>-0.04310740859408292</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="AG7">
-        <v>-34.7</v>
+        <v>66.5</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>0.2655565293602103</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>0.2577992058990357</v>
       </c>
       <c r="AJ7">
-        <v>-0.2253246753246753</v>
+        <v>0.2091852783894307</v>
       </c>
       <c r="AK7">
-        <v>-0.2558997050147492</v>
+        <v>0.2026203534430226</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>6.356643356643357</v>
+      </c>
+      <c r="AO7">
+        <v>5.054945054945056</v>
       </c>
       <c r="AP7">
-        <v>-2.478571428571429</v>
+        <v>4.65034965034965</v>
+      </c>
+      <c r="AQ7">
+        <v>5.054945054945056</v>
       </c>
     </row>
     <row r="8">
@@ -1356,7 +1362,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Oman Insurance Company P.S.C. (DFM:OIC)</t>
+          <t>Emirates Insurance Company P.J.S.C. (ADX:EIC)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1365,46 +1371,46 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0391</v>
+        <v>-0.0454</v>
       </c>
       <c r="E8">
-        <v>0.293</v>
+        <v>-0.204</v>
       </c>
       <c r="G8">
-        <v>0.134809294169224</v>
+        <v>0.1677115987460815</v>
       </c>
       <c r="H8">
-        <v>0.134809294169224</v>
+        <v>0.1677115987460815</v>
       </c>
       <c r="I8">
-        <v>0.128233231039018</v>
+        <v>0.0755485893416928</v>
       </c>
       <c r="J8">
-        <v>0.1270446076282332</v>
+        <v>0.0755485893416928</v>
       </c>
       <c r="K8">
-        <v>51.5</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>0.1128890837352039</v>
+        <v>0.07053291536050157</v>
       </c>
       <c r="M8">
-        <v>25.1</v>
+        <v>20.4</v>
       </c>
       <c r="N8">
-        <v>0.07678189048638728</v>
+        <v>0.07346056895930861</v>
       </c>
       <c r="O8">
-        <v>0.4873786407766991</v>
+        <v>2.266666666666667</v>
       </c>
       <c r="P8">
-        <v>25.1</v>
+        <v>20.4</v>
       </c>
       <c r="Q8">
-        <v>0.07678189048638728</v>
+        <v>0.07346056895930861</v>
       </c>
       <c r="R8">
-        <v>0.4873786407766991</v>
+        <v>2.266666666666667</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1413,31 +1419,31 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>74.7</v>
+        <v>20</v>
       </c>
       <c r="V8">
-        <v>0.2285102477821964</v>
+        <v>0.07202016564638099</v>
       </c>
       <c r="W8">
-        <v>0.09501845018450185</v>
+        <v>0.02895752895752896</v>
       </c>
       <c r="X8">
-        <v>0.04734017771778325</v>
+        <v>0.08020795072631406</v>
       </c>
       <c r="Y8">
-        <v>0.0476782724667186</v>
+        <v>-0.05125042176878511</v>
       </c>
       <c r="Z8">
-        <v>0.9507732066191489</v>
+        <v>0.4754098360655737</v>
       </c>
       <c r="AA8">
-        <v>0.1207906089783669</v>
+        <v>0.03591654247391952</v>
       </c>
       <c r="AB8">
-        <v>0.04734017771778325</v>
+        <v>0.08020795072631406</v>
       </c>
       <c r="AC8">
-        <v>0.07345043126058362</v>
+        <v>-0.04429140825239455</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -1449,7 +1455,7 @@
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>-74.7</v>
+        <v>-20</v>
       </c>
       <c r="AH8">
         <v>0</v>
@@ -1458,10 +1464,10 @@
         <v>0</v>
       </c>
       <c r="AJ8">
-        <v>-0.2961934972244251</v>
+        <v>-0.07760962359332557</v>
       </c>
       <c r="AK8">
-        <v>-0.1450203843913803</v>
+        <v>-0.07246376811594203</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1473,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>-1.228618421052632</v>
+        <v>-1.851851851851852</v>
       </c>
     </row>
     <row r="9">
@@ -1484,7 +1490,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Union Insurance Company P.J.S.C. (ADX:UNION)</t>
+          <t>Methaq Takaful Insurance P.S.C. (ADX:METHAQ)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1493,25 +1499,25 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.00368</v>
+        <v>-0.0133</v>
       </c>
       <c r="G9">
-        <v>0.03433515482695811</v>
+        <v>-0.1194915254237288</v>
       </c>
       <c r="H9">
-        <v>0.03433515482695811</v>
+        <v>-0.1194915254237288</v>
       </c>
       <c r="I9">
-        <v>0.0790528233151184</v>
+        <v>-0.2101694915254237</v>
       </c>
       <c r="J9">
-        <v>0.0790528233151184</v>
+        <v>-0.2101694915254237</v>
       </c>
       <c r="K9">
-        <v>8.57</v>
+        <v>-7.13</v>
       </c>
       <c r="L9">
-        <v>0.07805100182149363</v>
+        <v>-0.1208474576271186</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1520,7 +1526,7 @@
         <v>-0</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1529,466 +1535,73 @@
         <v>-0</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>5.67</v>
+        <v>0.506</v>
       </c>
       <c r="V9">
-        <v>0.08736517719568566</v>
+        <v>0.01946153846153846</v>
       </c>
       <c r="W9">
-        <v>0.09816723940435282</v>
+        <v>-0.2875</v>
       </c>
       <c r="X9">
-        <v>0.04748972942043254</v>
+        <v>0.1665276018557841</v>
       </c>
       <c r="Y9">
-        <v>0.05067750998392028</v>
+        <v>-0.4540276018557841</v>
       </c>
       <c r="Z9">
-        <v>1.435782095875722</v>
+        <v>0.825405707890319</v>
       </c>
       <c r="AA9">
-        <v>0.1135026283442739</v>
+        <v>-0.1734750979294908</v>
       </c>
       <c r="AB9">
-        <v>0.04716695684520979</v>
+        <v>0.09780599346350777</v>
       </c>
       <c r="AC9">
-        <v>0.06633567149906408</v>
+        <v>-0.2712810913929985</v>
       </c>
       <c r="AD9">
-        <v>0.669</v>
+        <v>54.2</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0.669</v>
+        <v>54.2</v>
       </c>
       <c r="AG9">
-        <v>-5.000999999999999</v>
+        <v>53.694</v>
       </c>
       <c r="AH9">
-        <v>0.01020299226768747</v>
+        <v>0.6758104738154613</v>
       </c>
       <c r="AI9">
-        <v>0.009945145609418901</v>
+        <v>0.7548746518105849</v>
       </c>
       <c r="AJ9">
-        <v>-0.08349054241306196</v>
+        <v>0.6737521017893443</v>
       </c>
       <c r="AK9">
-        <v>-0.08118638289582622</v>
+        <v>0.7531349061632114</v>
       </c>
       <c r="AL9">
-        <v>0.063</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>0.063</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>0.07005235602094241</v>
-      </c>
-      <c r="AO9">
-        <v>137.7777777777778</v>
+        <v>-4.479338842975207</v>
       </c>
       <c r="AP9">
-        <v>-0.5236649214659684</v>
-      </c>
-      <c r="AQ9">
-        <v>137.7777777777778</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Sharjah Insurance Company P.S.C. (ADX:SICO)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>-0.06849999999999999</v>
-      </c>
-      <c r="G10">
-        <v>0.4368098159509202</v>
-      </c>
-      <c r="H10">
-        <v>0.4368098159509202</v>
-      </c>
-      <c r="I10">
-        <v>0.6515337423312882</v>
-      </c>
-      <c r="J10">
-        <v>0.6515337423312882</v>
-      </c>
-      <c r="K10">
-        <v>5.03</v>
-      </c>
-      <c r="L10">
-        <v>0.6171779141104294</v>
-      </c>
-      <c r="M10">
-        <v>2.62</v>
-      </c>
-      <c r="N10">
-        <v>0.06599496221662468</v>
-      </c>
-      <c r="O10">
-        <v>0.5208747514910537</v>
-      </c>
-      <c r="P10">
-        <v>2.62</v>
-      </c>
-      <c r="Q10">
-        <v>0.06599496221662468</v>
-      </c>
-      <c r="R10">
-        <v>0.5208747514910537</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>5.92</v>
-      </c>
-      <c r="V10">
-        <v>0.1491183879093199</v>
-      </c>
-      <c r="W10">
-        <v>0.1081720430107527</v>
-      </c>
-      <c r="X10">
-        <v>0.04955841563808867</v>
-      </c>
-      <c r="Y10">
-        <v>0.05861362737266403</v>
-      </c>
-      <c r="Z10">
-        <v>0.169855362427577</v>
-      </c>
-      <c r="AA10">
-        <v>0.1106664999374765</v>
-      </c>
-      <c r="AB10">
-        <v>0.04508863369363385</v>
-      </c>
-      <c r="AC10">
-        <v>0.06557786624384268</v>
-      </c>
-      <c r="AD10">
-        <v>6.07</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>6.07</v>
-      </c>
-      <c r="AG10">
-        <v>0.1500000000000004</v>
-      </c>
-      <c r="AH10">
-        <v>0.132619619838322</v>
-      </c>
-      <c r="AI10">
-        <v>0.09639510878195967</v>
-      </c>
-      <c r="AJ10">
-        <v>0.003764115432873283</v>
-      </c>
-      <c r="AK10">
-        <v>0.002629272567922881</v>
-      </c>
-      <c r="AL10">
-        <v>0.047</v>
-      </c>
-      <c r="AM10">
-        <v>0.047</v>
-      </c>
-      <c r="AN10">
-        <v>1.132462686567164</v>
-      </c>
-      <c r="AO10">
-        <v>112.9787234042553</v>
-      </c>
-      <c r="AP10">
-        <v>0.02798507462686574</v>
-      </c>
-      <c r="AQ10">
-        <v>112.9787234042553</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Al Buhaira National Insurance Company P.S.C. (ADX:ABNIC)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>-0.0451</v>
-      </c>
-      <c r="E11">
-        <v>-0.189</v>
-      </c>
-      <c r="G11">
-        <v>0.2012072434607646</v>
-      </c>
-      <c r="H11">
-        <v>0.2012072434607646</v>
-      </c>
-      <c r="I11">
-        <v>0.1670020120724346</v>
-      </c>
-      <c r="J11">
-        <v>0.1670020120724346</v>
-      </c>
-      <c r="K11">
-        <v>4.65</v>
-      </c>
-      <c r="L11">
-        <v>0.04678068410462777</v>
-      </c>
-      <c r="M11">
-        <v>6.81</v>
-      </c>
-      <c r="N11">
-        <v>0.05266821345707656</v>
-      </c>
-      <c r="O11">
-        <v>1.464516129032258</v>
-      </c>
-      <c r="P11">
-        <v>6.81</v>
-      </c>
-      <c r="Q11">
-        <v>0.05266821345707656</v>
-      </c>
-      <c r="R11">
-        <v>1.464516129032258</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>5.28</v>
-      </c>
-      <c r="V11">
-        <v>0.04083526682134571</v>
-      </c>
-      <c r="W11">
-        <v>0.0246684350132626</v>
-      </c>
-      <c r="X11">
-        <v>0.05507108808236074</v>
-      </c>
-      <c r="Y11">
-        <v>-0.03040265306909814</v>
-      </c>
-      <c r="Z11">
-        <v>0.3722846441947566</v>
-      </c>
-      <c r="AA11">
-        <v>0.06217228464419476</v>
-      </c>
-      <c r="AB11">
-        <v>0.0414383267826052</v>
-      </c>
-      <c r="AC11">
-        <v>0.02073395786158956</v>
-      </c>
-      <c r="AD11">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="AG11">
-        <v>63.62</v>
-      </c>
-      <c r="AH11">
-        <v>0.3476286579212916</v>
-      </c>
-      <c r="AI11">
-        <v>0.2687207488299532</v>
-      </c>
-      <c r="AJ11">
-        <v>0.3297739995853203</v>
-      </c>
-      <c r="AK11">
-        <v>0.2533450143357757</v>
-      </c>
-      <c r="AL11">
-        <v>3.61</v>
-      </c>
-      <c r="AM11">
-        <v>3.61</v>
-      </c>
-      <c r="AN11">
-        <v>4.076923076923078</v>
-      </c>
-      <c r="AO11">
-        <v>4.598337950138505</v>
-      </c>
-      <c r="AP11">
-        <v>3.764497041420119</v>
-      </c>
-      <c r="AQ11">
-        <v>4.598337950138505</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Methaq Takaful Insurance Company PSC (ADX:METHAQ)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>-0.00728</v>
-      </c>
-      <c r="G12">
-        <v>0.04403669724770642</v>
-      </c>
-      <c r="H12">
-        <v>0.04403669724770642</v>
-      </c>
-      <c r="I12">
-        <v>-0.09908256880733946</v>
-      </c>
-      <c r="J12">
-        <v>-0.09908256880733946</v>
-      </c>
-      <c r="K12">
-        <v>-5.4</v>
-      </c>
-      <c r="L12">
-        <v>-0.09908256880733946</v>
-      </c>
-      <c r="M12">
-        <v>-0</v>
-      </c>
-      <c r="N12">
-        <v>-0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>-0</v>
-      </c>
-      <c r="Q12">
-        <v>-0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>1.89</v>
-      </c>
-      <c r="V12">
-        <v>0.05709969788519637</v>
-      </c>
-      <c r="W12">
-        <v>-0.2068965517241379</v>
-      </c>
-      <c r="X12">
-        <v>0.06934336849254831</v>
-      </c>
-      <c r="Y12">
-        <v>-0.2762399202166863</v>
-      </c>
-      <c r="Z12">
-        <v>0.7693393562958781</v>
-      </c>
-      <c r="AA12">
-        <v>-0.07622811970638059</v>
-      </c>
-      <c r="AB12">
-        <v>0.03503032813348058</v>
-      </c>
-      <c r="AC12">
-        <v>-0.1112584478398612</v>
-      </c>
-      <c r="AD12">
-        <v>50.2</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>50.2</v>
-      </c>
-      <c r="AG12">
-        <v>48.31</v>
-      </c>
-      <c r="AH12">
-        <v>0.6026410564225689</v>
-      </c>
-      <c r="AI12">
-        <v>0.7080394922425952</v>
-      </c>
-      <c r="AJ12">
-        <v>0.5934160422552512</v>
-      </c>
-      <c r="AK12">
-        <v>0.7000434719605854</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>-9.709864603481625</v>
-      </c>
-      <c r="AP12">
-        <v>-9.344294003868473</v>
+        <v>-4.437520661157025</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0133</v>
+        <v>0.03695</v>
       </c>
       <c r="E2">
-        <v>0.03736</v>
+        <v>0.06955</v>
       </c>
       <c r="G2">
-        <v>0.2260232536156536</v>
+        <v>0.1355118160392382</v>
       </c>
       <c r="H2">
-        <v>0.2260232536156536</v>
+        <v>0.1355118160392382</v>
       </c>
       <c r="I2">
-        <v>0.1306172606106437</v>
+        <v>0.1117130507656296</v>
       </c>
       <c r="J2">
-        <v>0.1306164439975733</v>
+        <v>0.111593022126226</v>
       </c>
       <c r="K2">
-        <v>133.45</v>
+        <v>165.64</v>
       </c>
       <c r="L2">
-        <v>0.126146138576425</v>
+        <v>0.1055099050894961</v>
       </c>
       <c r="M2">
-        <v>118.3</v>
+        <v>117.8</v>
       </c>
       <c r="N2">
-        <v>0.06422018348623852</v>
+        <v>0.05479324619749756</v>
       </c>
       <c r="O2">
-        <v>0.8864743349569125</v>
+        <v>0.7111808741849796</v>
       </c>
       <c r="P2">
-        <v>118.3</v>
+        <v>117.8</v>
       </c>
       <c r="Q2">
-        <v>0.06422018348623852</v>
+        <v>0.05479324619749756</v>
       </c>
       <c r="R2">
-        <v>0.8864743349569125</v>
+        <v>0.7111808741849796</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>291.156</v>
+        <v>391.09</v>
       </c>
       <c r="V2">
-        <v>0.1580565658759025</v>
+        <v>0.1819107865482115</v>
       </c>
       <c r="W2">
-        <v>0.04036535061873895</v>
+        <v>0.1033683427171045</v>
       </c>
       <c r="X2">
-        <v>0.08056212598559234</v>
+        <v>0.07212351434845192</v>
       </c>
       <c r="Y2">
-        <v>-0.04019677536685339</v>
+        <v>0.03124482836865257</v>
       </c>
       <c r="Z2">
-        <v>0.6071932222106793</v>
+        <v>1.039594238180156</v>
       </c>
       <c r="AA2">
-        <v>0.04389248043552229</v>
+        <v>0.1272194956988854</v>
       </c>
       <c r="AB2">
-        <v>0.08042878936996081</v>
+        <v>0.07189913954612441</v>
       </c>
       <c r="AC2">
-        <v>-0.03631547029079178</v>
+        <v>0.05550274509962078</v>
       </c>
       <c r="AD2">
-        <v>155.41</v>
+        <v>103.19</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.3484080151900734</v>
       </c>
       <c r="AF2">
-        <v>155.41</v>
+        <v>103.5384080151901</v>
       </c>
       <c r="AG2">
-        <v>-135.746</v>
+        <v>-287.5515919848099</v>
       </c>
       <c r="AH2">
-        <v>0.07780186331983319</v>
+        <v>0.04594685510237035</v>
       </c>
       <c r="AI2">
-        <v>0.07792279420981643</v>
+        <v>0.0449534045867245</v>
       </c>
       <c r="AJ2">
-        <v>-0.07955324627832208</v>
+        <v>-0.1544026835941347</v>
       </c>
       <c r="AK2">
-        <v>-0.07969803681658755</v>
+        <v>-0.1503814195485425</v>
       </c>
       <c r="AL2">
-        <v>2.958</v>
+        <v>11.373</v>
       </c>
       <c r="AM2">
-        <v>2.958</v>
+        <v>11.373</v>
       </c>
       <c r="AN2">
-        <v>1.029887342611001</v>
+        <v>0.555358219237062</v>
       </c>
       <c r="AO2">
-        <v>46.71399594320486</v>
+        <v>15.39435505143762</v>
       </c>
       <c r="AP2">
-        <v>-0.8995758780649437</v>
+        <v>-1.547573796525499</v>
       </c>
       <c r="AQ2">
-        <v>46.71399594320486</v>
+        <v>15.39435505143762</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Abu Dhabi National Insurance Company PJSC (ADX:ADNIC)</t>
+          <t>Emirates Insurance Company P.J.S.C. (ADX:EIC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0607</v>
+        <v>-0.0386</v>
       </c>
       <c r="E3">
-        <v>0.06950000000000001</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="G3">
-        <v>0.2423933020216459</v>
+        <v>0.1586826347305389</v>
       </c>
       <c r="H3">
-        <v>0.2423933020216459</v>
+        <v>0.1586826347305389</v>
       </c>
       <c r="I3">
-        <v>0.1917500510516643</v>
+        <v>0.1497005988023952</v>
       </c>
       <c r="J3">
-        <v>0.1917416593645286</v>
+        <v>0.1497005988023952</v>
       </c>
       <c r="K3">
-        <v>91.40000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="L3">
-        <v>0.1866448846232387</v>
+        <v>0.1459580838323353</v>
       </c>
       <c r="M3">
-        <v>62.1</v>
+        <v>20.4</v>
       </c>
       <c r="N3">
-        <v>0.06453959675743089</v>
+        <v>0.06986301369863013</v>
       </c>
       <c r="O3">
-        <v>0.6794310722100656</v>
+        <v>1.046153846153846</v>
       </c>
       <c r="P3">
-        <v>62.1</v>
+        <v>20.4</v>
       </c>
       <c r="Q3">
-        <v>0.06453959675743089</v>
+        <v>0.06986301369863013</v>
       </c>
       <c r="R3">
-        <v>0.6794310722100656</v>
+        <v>1.046153846153846</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,55 +770,40 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>161.7</v>
+        <v>17.9</v>
       </c>
       <c r="V3">
-        <v>0.1680523799625857</v>
-      </c>
-      <c r="W3">
-        <v>0.1236137408709765</v>
+        <v>0.0613013698630137</v>
       </c>
       <c r="X3">
-        <v>0.08056212598559234</v>
-      </c>
-      <c r="Y3">
-        <v>0.04305161488538414</v>
-      </c>
-      <c r="Z3">
-        <v>0.8288761002031144</v>
-      </c>
-      <c r="AA3">
-        <v>0.1589300788605444</v>
+        <v>0.0719277578049938</v>
       </c>
       <c r="AB3">
-        <v>0.08042878936996081</v>
-      </c>
-      <c r="AC3">
-        <v>0.0785012894905836</v>
+        <v>0.0719277578049938</v>
       </c>
       <c r="AD3">
-        <v>8.23</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>8.23</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-153.47</v>
+        <v>-17.9</v>
       </c>
       <c r="AH3">
-        <v>0.008480776562966932</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.01155687865979526</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.1897666712005243</v>
+        <v>-0.06530463334549433</v>
       </c>
       <c r="AK3">
-        <v>-0.2788183783587377</v>
+        <v>-0.05700636942675159</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -827,10 +812,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.08304742684157418</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>-1.548637739656912</v>
+        <v>-0.8443396226415094</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>National General Insurance Co. (P.J.S.C.) (DFM:NGI)</t>
+          <t>Abu Dhabi National Insurance Company PJSC (ADX:ADNIC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,46 +835,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0194</v>
+        <v>0.0142</v>
       </c>
       <c r="E4">
-        <v>0.12</v>
+        <v>0.0944</v>
       </c>
       <c r="G4">
-        <v>0.1993927125506073</v>
+        <v>0.2129109863672815</v>
       </c>
       <c r="H4">
-        <v>0.1993927125506073</v>
+        <v>0.2129109863672815</v>
       </c>
       <c r="I4">
-        <v>0.1609311740890688</v>
+        <v>0.22514033680834</v>
       </c>
       <c r="J4">
-        <v>0.1609311740890688</v>
+        <v>0.225130488149687</v>
       </c>
       <c r="K4">
-        <v>15.9</v>
+        <v>114.3</v>
       </c>
       <c r="L4">
-        <v>0.1609311740890688</v>
+        <v>0.229149959903769</v>
       </c>
       <c r="M4">
-        <v>12.2</v>
+        <v>62.1</v>
       </c>
       <c r="N4">
-        <v>0.09166040570999248</v>
+        <v>0.06703367875647669</v>
       </c>
       <c r="O4">
-        <v>0.7672955974842767</v>
+        <v>0.5433070866141733</v>
       </c>
       <c r="P4">
-        <v>12.2</v>
+        <v>62.1</v>
       </c>
       <c r="Q4">
-        <v>0.09166040570999248</v>
+        <v>0.06703367875647669</v>
       </c>
       <c r="R4">
-        <v>0.7672955974842767</v>
+        <v>0.5433070866141733</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,55 +883,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>9.75</v>
+        <v>254.2</v>
       </c>
       <c r="V4">
-        <v>0.07325319308790383</v>
+        <v>0.2743955094991364</v>
       </c>
       <c r="W4">
-        <v>0.1129261363636364</v>
+        <v>0.1623810200312544</v>
       </c>
       <c r="X4">
-        <v>0.08020795072631406</v>
+        <v>0.07217154935166428</v>
       </c>
       <c r="Y4">
-        <v>0.03271818563732229</v>
+        <v>0.09020947067959015</v>
       </c>
       <c r="Z4">
-        <v>0.8288590604026845</v>
+        <v>0.9062006067983213</v>
       </c>
       <c r="AA4">
-        <v>0.1333892617449664</v>
+        <v>0.2040133849700486</v>
       </c>
       <c r="AB4">
-        <v>0.08020795072631406</v>
+        <v>0.07189952523368261</v>
       </c>
       <c r="AC4">
-        <v>0.05318131101865237</v>
+        <v>0.132113859736366</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="AG4">
-        <v>-9.75</v>
+        <v>-245.11</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.009716832889715549</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.01169297263921584</v>
       </c>
       <c r="AJ4">
-        <v>-0.0790433725172274</v>
+        <v>-0.3597733711048159</v>
       </c>
       <c r="AK4">
-        <v>-0.07520246818357115</v>
+        <v>-0.4684913702479023</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -955,10 +940,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>0.07716468590831918</v>
       </c>
       <c r="AP4">
-        <v>-0.6018518518518519</v>
+        <v>-2.080730050933786</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Union Insurance Company P.J.S.C. (ADX:UNION)</t>
+          <t>National General Insurance Co. (P.J.S.C.) (DFM:NGI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -978,112 +963,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0441</v>
+        <v>0.0696</v>
       </c>
       <c r="E5">
-        <v>0.132</v>
+        <v>0.0447</v>
       </c>
       <c r="G5">
-        <v>0.04584103512014787</v>
+        <v>0.1254180602006689</v>
       </c>
       <c r="H5">
-        <v>0.04584103512014787</v>
+        <v>0.1254180602006689</v>
       </c>
       <c r="I5">
-        <v>0.04103512014787431</v>
+        <v>0.1697324414715719</v>
       </c>
       <c r="J5">
-        <v>0.04103512014787431</v>
+        <v>0.1697324414715719</v>
       </c>
       <c r="K5">
-        <v>4.44</v>
+        <v>17.1</v>
       </c>
       <c r="L5">
-        <v>0.04103512014787431</v>
+        <v>0.1429765886287626</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>10.2</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.05315268368942157</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.5964912280701753</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>10.2</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.05315268368942157</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.5964912280701753</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>43.7</v>
+        <v>20.9</v>
       </c>
       <c r="V5">
-        <v>0.7680140597539544</v>
+        <v>0.1089108910891089</v>
       </c>
       <c r="W5">
-        <v>0.06666666666666668</v>
+        <v>0.1226685796269728</v>
       </c>
       <c r="X5">
-        <v>0.08172163328362045</v>
+        <v>0.0719277578049938</v>
       </c>
       <c r="Y5">
-        <v>-0.01505496661695377</v>
+        <v>0.05074082182197895</v>
       </c>
       <c r="Z5">
-        <v>1.756522021461388</v>
+        <v>0.9224836097184728</v>
       </c>
       <c r="AA5">
-        <v>0.0720790921930551</v>
+        <v>0.1565753952950251</v>
       </c>
       <c r="AB5">
-        <v>0.08099226759939497</v>
+        <v>0.0719277578049938</v>
       </c>
       <c r="AC5">
-        <v>-0.008913175406339874</v>
+        <v>0.08464763749003126</v>
       </c>
       <c r="AD5">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>-41.62</v>
+        <v>-20.9</v>
       </c>
       <c r="AH5">
-        <v>0.03526619192946762</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.02838427947598253</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-2.723821989528797</v>
+        <v>-0.1222222222222222</v>
       </c>
       <c r="AK5">
-        <v>-1.407031778228533</v>
+        <v>-0.1601532567049808</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AN5">
-        <v>0.3586206896551725</v>
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>6.506410256410256</v>
       </c>
       <c r="AP5">
-        <v>-7.175862068965518</v>
+        <v>-1.004807692307692</v>
+      </c>
+      <c r="AQ5">
+        <v>6.506410256410256</v>
       </c>
     </row>
     <row r="6">
@@ -1094,7 +1088,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Al Ain Ahlia Insurance Company P.S.C. (ADX:ALAIN)</t>
+          <t>Oman Insurance Company P.S.C. (DFM:OIC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1103,46 +1097,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0441</v>
+        <v>0.0597</v>
       </c>
       <c r="E6">
-        <v>0.00522</v>
+        <v>0.135</v>
       </c>
       <c r="G6">
-        <v>0.2721649484536082</v>
+        <v>0.1184810126582279</v>
       </c>
       <c r="H6">
-        <v>0.2721649484536082</v>
+        <v>0.1184810126582279</v>
       </c>
       <c r="I6">
-        <v>0.1329896907216495</v>
+        <v>0.09383966244725739</v>
       </c>
       <c r="J6">
-        <v>0.1329896907216495</v>
+        <v>0.09323881856540084</v>
       </c>
       <c r="K6">
-        <v>13.7</v>
+        <v>55.3</v>
       </c>
       <c r="L6">
-        <v>0.1412371134020619</v>
+        <v>0.09333333333333332</v>
       </c>
       <c r="M6">
-        <v>12.3</v>
+        <v>25.1</v>
       </c>
       <c r="N6">
-        <v>0.09124629080118694</v>
+        <v>0.05118270799347472</v>
       </c>
       <c r="O6">
-        <v>0.8978102189781023</v>
+        <v>0.4538878842676312</v>
       </c>
       <c r="P6">
-        <v>12.3</v>
+        <v>25.1</v>
       </c>
       <c r="Q6">
-        <v>0.09124629080118694</v>
+        <v>0.05118270799347472</v>
       </c>
       <c r="R6">
-        <v>0.8978102189781023</v>
+        <v>0.4538878842676312</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1151,73 +1145,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>31.1</v>
+        <v>86.2</v>
       </c>
       <c r="V6">
-        <v>0.2307121661721068</v>
+        <v>0.1757748776508972</v>
       </c>
       <c r="W6">
-        <v>0.04036535061873895</v>
+        <v>0.08406810580723624</v>
       </c>
       <c r="X6">
-        <v>0.08020795072631406</v>
+        <v>0.07311330460246043</v>
       </c>
       <c r="Y6">
-        <v>-0.03984260010757511</v>
+        <v>0.01095480120477581</v>
       </c>
       <c r="Z6">
-        <v>0.3300442327322219</v>
+        <v>1.049601417183348</v>
       </c>
       <c r="AA6">
-        <v>0.04389248043552229</v>
+        <v>0.0978635961027458</v>
       </c>
       <c r="AB6">
-        <v>0.08020795072631406</v>
+        <v>0.07150574339353551</v>
       </c>
       <c r="AC6">
-        <v>-0.03631547029079178</v>
+        <v>0.02635785270921029</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="AG6">
-        <v>-31.1</v>
+        <v>-62.8</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.04554301284546516</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.03057224980402404</v>
       </c>
       <c r="AJ6">
-        <v>-0.2999035679845709</v>
+        <v>-0.146866230121609</v>
       </c>
       <c r="AK6">
-        <v>-0.09776799748506761</v>
+        <v>-0.09246171967020024</v>
       </c>
       <c r="AL6">
-        <v>0.228</v>
+        <v>0.523</v>
       </c>
       <c r="AM6">
-        <v>0.228</v>
+        <v>0.523</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>0.4112478031634446</v>
       </c>
       <c r="AO6">
-        <v>56.57894736842105</v>
+        <v>106.3097514340344</v>
       </c>
       <c r="AP6">
-        <v>-1.851190476190476</v>
+        <v>-1.103690685413005</v>
       </c>
       <c r="AQ6">
-        <v>56.57894736842105</v>
+        <v>106.3097514340344</v>
       </c>
     </row>
     <row r="7">
@@ -1228,7 +1222,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Al Wathba National Insurance Company PJSC (ADX:AWNIC)</t>
+          <t>Union Insurance Company P.J.S.C. (ADX:UNION)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1237,121 +1231,115 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0357</v>
-      </c>
-      <c r="E7">
-        <v>-0.17</v>
+        <v>-0.08130000000000001</v>
       </c>
       <c r="G7">
-        <v>0.7087628865979382</v>
+        <v>0.06796628029504742</v>
       </c>
       <c r="H7">
-        <v>0.7087628865979382</v>
+        <v>0.06796628029504742</v>
       </c>
       <c r="I7">
-        <v>0.1778350515463918</v>
+        <v>0.01136268068453093</v>
       </c>
       <c r="J7">
-        <v>0.1778350515463918</v>
+        <v>0.01136268068453093</v>
       </c>
       <c r="K7">
-        <v>6.14</v>
+        <v>-2.86</v>
       </c>
       <c r="L7">
-        <v>0.07912371134020618</v>
+        <v>-0.03013698630136986</v>
       </c>
       <c r="M7">
-        <v>11.3</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.04494828957836118</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>1.840390879478828</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>11.3</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.04494828957836118</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>1.840390879478828</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>24.4</v>
+        <v>5.22</v>
       </c>
       <c r="V7">
-        <v>0.09705648369132855</v>
+        <v>0.08907849829351536</v>
       </c>
       <c r="W7">
-        <v>0.02386319471434123</v>
+        <v>-0.0401685393258427</v>
       </c>
       <c r="X7">
-        <v>0.09518003792210541</v>
+        <v>0.07207547934523956</v>
       </c>
       <c r="Y7">
-        <v>-0.07131684320776419</v>
+        <v>-0.1122440186710822</v>
       </c>
       <c r="Z7">
-        <v>0.2303354111012169</v>
+        <v>3.170900368366864</v>
       </c>
       <c r="AA7">
-        <v>0.04096170970614425</v>
+        <v>0.03602992836821418</v>
       </c>
       <c r="AB7">
-        <v>0.08406911830022717</v>
+        <v>0.07189875385856621</v>
       </c>
       <c r="AC7">
-        <v>-0.04310740859408292</v>
+        <v>-0.03586882549035204</v>
       </c>
       <c r="AD7">
-        <v>90.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>0.3484080151900734</v>
       </c>
       <c r="AF7">
-        <v>90.90000000000001</v>
+        <v>0.3484080151900734</v>
       </c>
       <c r="AG7">
-        <v>66.5</v>
+        <v>-4.871591984809927</v>
       </c>
       <c r="AH7">
-        <v>0.2655565293602103</v>
+        <v>0.005910388879378966</v>
       </c>
       <c r="AI7">
-        <v>0.2577992058990357</v>
+        <v>0.006064711403281183</v>
       </c>
       <c r="AJ7">
-        <v>0.2091852783894307</v>
+        <v>-0.09067069293087247</v>
       </c>
       <c r="AK7">
-        <v>0.2026203534430226</v>
+        <v>-0.09327475544330349</v>
       </c>
       <c r="AL7">
-        <v>2.73</v>
+        <v>3.64</v>
       </c>
       <c r="AM7">
-        <v>2.73</v>
+        <v>3.64</v>
       </c>
       <c r="AN7">
-        <v>6.356643356643357</v>
+        <v>0</v>
       </c>
       <c r="AO7">
-        <v>5.054945054945056</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="AP7">
-        <v>4.65034965034965</v>
+        <v>-2.023086372429372</v>
       </c>
       <c r="AQ7">
-        <v>5.054945054945056</v>
+        <v>0.2142857142857143</v>
       </c>
     </row>
     <row r="8">
@@ -1362,7 +1350,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Emirates Insurance Company P.J.S.C. (ADX:EIC)</t>
+          <t>Al Buhaira National Insurance Company P.S.C. (ADX:ABNIC)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1371,237 +1359,115 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.0454</v>
-      </c>
-      <c r="E8">
-        <v>-0.204</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="G8">
-        <v>0.1677115987460815</v>
+        <v>-0.04835249042145594</v>
       </c>
       <c r="H8">
-        <v>0.1677115987460815</v>
+        <v>-0.04835249042145594</v>
       </c>
       <c r="I8">
-        <v>0.0755485893416928</v>
+        <v>-0.2597701149425287</v>
       </c>
       <c r="J8">
-        <v>0.0755485893416928</v>
+        <v>-0.2597701149425287</v>
       </c>
       <c r="K8">
-        <v>9</v>
+        <v>-37.7</v>
       </c>
       <c r="L8">
-        <v>0.07053291536050157</v>
+        <v>-0.2888888888888889</v>
       </c>
       <c r="M8">
-        <v>20.4</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.07346056895930861</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>2.266666666666667</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>20.4</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.07346056895930861</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>2.266666666666667</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>20</v>
+        <v>6.67</v>
       </c>
       <c r="V8">
-        <v>0.07202016564638099</v>
+        <v>0.03499475341028332</v>
       </c>
       <c r="W8">
-        <v>0.02895752895752896</v>
+        <v>-0.2047800108636611</v>
       </c>
       <c r="X8">
-        <v>0.08020795072631406</v>
+        <v>0.08114391393096335</v>
       </c>
       <c r="Y8">
-        <v>-0.05125042176878511</v>
+        <v>-0.2859239247946244</v>
       </c>
       <c r="Z8">
-        <v>0.4754098360655737</v>
+        <v>0.553904923599321</v>
       </c>
       <c r="AA8">
-        <v>0.03591654247391952</v>
+        <v>-0.1438879456706282</v>
       </c>
       <c r="AB8">
-        <v>0.08020795072631406</v>
+        <v>0.07114160728855334</v>
       </c>
       <c r="AC8">
-        <v>-0.04429140825239455</v>
+        <v>-0.2150295529591816</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>70.7</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>70.7</v>
       </c>
       <c r="AG8">
-        <v>-20</v>
+        <v>64.03</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>0.2705702257941064</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>0.3218024578971325</v>
       </c>
       <c r="AJ8">
-        <v>-0.07760962359332557</v>
+        <v>0.2514629069630444</v>
       </c>
       <c r="AK8">
-        <v>-0.07246376811594203</v>
+        <v>0.3005679951180585</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>-2.123123123123123</v>
+      </c>
+      <c r="AO8">
+        <v>-8.288508557457213</v>
       </c>
       <c r="AP8">
-        <v>-1.851851851851852</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Methaq Takaful Insurance P.S.C. (ADX:METHAQ)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>-0.0133</v>
-      </c>
-      <c r="G9">
-        <v>-0.1194915254237288</v>
-      </c>
-      <c r="H9">
-        <v>-0.1194915254237288</v>
-      </c>
-      <c r="I9">
-        <v>-0.2101694915254237</v>
-      </c>
-      <c r="J9">
-        <v>-0.2101694915254237</v>
-      </c>
-      <c r="K9">
-        <v>-7.13</v>
-      </c>
-      <c r="L9">
-        <v>-0.1208474576271186</v>
-      </c>
-      <c r="M9">
-        <v>-0</v>
-      </c>
-      <c r="N9">
-        <v>-0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>-0</v>
-      </c>
-      <c r="Q9">
-        <v>-0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0.506</v>
-      </c>
-      <c r="V9">
-        <v>0.01946153846153846</v>
-      </c>
-      <c r="W9">
-        <v>-0.2875</v>
-      </c>
-      <c r="X9">
-        <v>0.1665276018557841</v>
-      </c>
-      <c r="Y9">
-        <v>-0.4540276018557841</v>
-      </c>
-      <c r="Z9">
-        <v>0.825405707890319</v>
-      </c>
-      <c r="AA9">
-        <v>-0.1734750979294908</v>
-      </c>
-      <c r="AB9">
-        <v>0.09780599346350777</v>
-      </c>
-      <c r="AC9">
-        <v>-0.2712810913929985</v>
-      </c>
-      <c r="AD9">
-        <v>54.2</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>54.2</v>
-      </c>
-      <c r="AG9">
-        <v>53.694</v>
-      </c>
-      <c r="AH9">
-        <v>0.6758104738154613</v>
-      </c>
-      <c r="AI9">
-        <v>0.7548746518105849</v>
-      </c>
-      <c r="AJ9">
-        <v>0.6737521017893443</v>
-      </c>
-      <c r="AK9">
-        <v>0.7531349061632114</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>0</v>
-      </c>
-      <c r="AN9">
-        <v>-4.479338842975207</v>
-      </c>
-      <c r="AP9">
-        <v>-4.437520661157025</v>
+        <v>-1.922822822822823</v>
+      </c>
+      <c r="AQ8">
+        <v>-8.288508557457213</v>
       </c>
     </row>
   </sheetData>
